--- a/results/5218_gauss.xlsx
+++ b/results/5218_gauss.xlsx
@@ -413,87 +413,159 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="n">
-        <v>0</v>
+        <v>-2.418</v>
       </c>
       <c r="B1" t="n">
-        <v>21.70258357630441</v>
+        <v>18.03148983942251</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.31</v>
+        <v>-2.1545</v>
       </c>
       <c r="B2" t="n">
-        <v>20.91655263319897</v>
+        <v>38.11893711736435</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.6355</v>
+        <v>-1.891</v>
       </c>
       <c r="B3" t="n">
-        <v>19.11972986173582</v>
+        <v>75.26252467322684</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.9455</v>
+        <v>-1.612</v>
       </c>
       <c r="B4" t="n">
-        <v>17.86259749171467</v>
+        <v>138.4677846046473</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1.271</v>
+        <v>-1.3485</v>
       </c>
       <c r="B5" t="n">
-        <v>14.82329845570745</v>
+        <v>219.8831034054366</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1.581</v>
+        <v>-1.085</v>
       </c>
       <c r="B6" t="n">
-        <v>10.38030292978477</v>
+        <v>313.4565425214034</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1.9065</v>
+        <v>-0.806</v>
       </c>
       <c r="B7" t="n">
-        <v>6.184013183375527</v>
+        <v>414.2583184154398</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2.2165</v>
+        <v>-0.5425</v>
       </c>
       <c r="B8" t="n">
-        <v>3.63395498018083</v>
+        <v>495.9989575488208</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2.542</v>
+        <v>-0.279</v>
       </c>
       <c r="B9" t="n">
-        <v>2.328688896661953</v>
+        <v>551.8430106876622</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>2.8675</v>
+        <v>0</v>
       </c>
       <c r="B10" t="n">
-        <v>0.9866566828879053</v>
+        <v>574.894768025631</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>0.2325</v>
+      </c>
+      <c r="B11" t="n">
+        <v>563.7751630347459</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>0.465</v>
+      </c>
+      <c r="B12" t="n">
+        <v>523.676937089838</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>0.713</v>
+      </c>
+      <c r="B13" t="n">
+        <v>451.6914365499593</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>0.9455</v>
+      </c>
+      <c r="B14" t="n">
+        <v>364.7629273595138</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>1.178</v>
+      </c>
+      <c r="B15" t="n">
+        <v>269.6418309615122</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>1.426</v>
+      </c>
+      <c r="B16" t="n">
+        <v>173.1559288472495</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>1.6585</v>
+      </c>
+      <c r="B17" t="n">
+        <v>98.56763821943768</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>1.891</v>
+      </c>
+      <c r="B18" t="n">
+        <v>47.23440677999979</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>2.139</v>
+      </c>
+      <c r="B19" t="n">
+        <v>17.8037223955509</v>
       </c>
     </row>
   </sheetData>
